--- a/excel_reports/backtest_compare/s14/compare_s14_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s14/compare_s14_M15_20260528_0800_20260608_1000.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 09:00:48</t>
+          <t>2026-06-19 17:47:50</t>
         </is>
       </c>
     </row>

--- a/excel_reports/backtest_compare/s14/compare_s14_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s14/compare_s14_M15_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 17:47:50</t>
+          <t>2026-06-21 19:02:40</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_NOT_REPLAYED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_TREND_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_NOT_REPLAYED:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_TREND_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -11026,7 +11026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11871,10 +11871,10 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>122.04</v>
+        <v>128.96</v>
       </c>
       <c r="F29" s="13" t="n">
         <v>46170.85421296296</v>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_PD_CLOSED_NO_REPLAY:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_PD_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -11920,94 +11920,94 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>LIVE_SIGNAL_NOT_REPLAYED:TIME_TOO_FAR</t>
+          <t>LIVE_HISTORICAL_TREND_SKIP_DRIFT:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>16.88</v>
+        <v>-6.92</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>46171.0937962963</v>
+        <v>46179.16667824074</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>46171.0937962963</v>
+        <v>46179.16667824074</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>bt_gap</t>
+          <t>live_gap</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>BT_SIGNAL_NO_LIVE_FILL:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>LIVE_SIGNAL_NOT_REPLAYED:TIME_TOO_FAR</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>35.61</v>
+        <v>16.88</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>46177.21875</v>
+        <v>46171.0937962963</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>46178.55208333334</v>
+        <v>46171.0937962963</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>mismatch_gap</t>
+          <t>bt_gap</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>PNL_DIFF_SAME_BUCKET</t>
+          <t>BT_SIGNAL_NO_LIVE_FILL:TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>12.38</v>
+        <v>35.61</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>46171.4062962963</v>
+        <v>46177.21875</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>46171.4062962963</v>
+        <v>46178.55208333334</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>trail_source_gap</t>
+          <t>mismatch_gap</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>- -&gt; M1</t>
+          <t>PNL_DIFF_SAME_BUCKET</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -12031,12 +12031,12 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>live_entry_comment</t>
+          <t>trail_source_gap</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>M15_S14_SS</t>
+          <t>- -&gt; M1</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>74.73999999999999</v>
+        <v>12.38</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>46171.0937962963</v>
+        <v>46171.4062962963</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>46175.86460648148</v>
+        <v>46171.4062962963</v>
       </c>
     </row>
     <row r="36">
@@ -12065,25 +12065,25 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>M15_S14_BS</t>
+          <t>M15_S14_SS</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>14.41</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>46170.85421296296</v>
+        <v>46171.0937962963</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>46176.69795138889</v>
+        <v>46175.86460648148</v>
       </c>
     </row>
     <row r="37">
@@ -12094,25 +12094,25 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>M15_S14_SE</t>
+          <t>M15_S14_BS</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>20.88</v>
+        <v>14.41</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>46171.5937962963</v>
+        <v>46170.85421296296</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>46175.62796296296</v>
+        <v>46176.69795138889</v>
       </c>
     </row>
     <row r="38">
@@ -12123,25 +12123,25 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>M15_S14_BE</t>
+          <t>M15_S14_SE</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>18.87</v>
+        <v>20.88</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>46174.44793981482</v>
+        <v>46171.5937962963</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>46174.67710648148</v>
+        <v>46175.62796296296</v>
       </c>
     </row>
     <row r="39">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>M15_S14_BSSH4</t>
+          <t>M15_S14_BE</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -12161,74 +12161,74 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>13.1</v>
+        <v>18.87</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>46179.00539351852</v>
+        <v>46174.44793981482</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>46181.29172453703</v>
+        <v>46174.67710648148</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>mismatch_entry_comment</t>
+          <t>live_entry_comment</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>M15_S14_SE</t>
+          <t>M15_S14_BSSH4</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>12.38</v>
+        <v>13.1</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>46171.4062962963</v>
+        <v>46179.00539351852</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>46171.4062962963</v>
+        <v>46181.29172453703</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>live_s14_family</t>
+          <t>mismatch_entry_comment</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>BUY_ENGULF</t>
+          <t>M15_S14_SE</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>31.97</v>
+        <v>12.38</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>46174.44793981482</v>
+        <v>46171.4062962963</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>46181.29172453703</v>
+        <v>46171.4062962963</v>
       </c>
     </row>
     <row r="42">
@@ -12239,25 +12239,25 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>SELL_SWEEP</t>
+          <t>BUY_ENGULF</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
         <v>9</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>74.73999999999999</v>
+        <v>31.97</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>46171.0937962963</v>
+        <v>46174.44793981482</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>46175.86460648148</v>
+        <v>46181.29172453703</v>
       </c>
     </row>
     <row r="43">
@@ -12268,25 +12268,25 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>BUY_SWEEP</t>
+          <t>SELL_SWEEP</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>14.41</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>46170.85421296296</v>
+        <v>46171.0937962963</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>46176.69795138889</v>
+        <v>46175.86460648148</v>
       </c>
     </row>
     <row r="44">
@@ -12297,94 +12297,94 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>SELL_ENGULF</t>
+          <t>BUY_SWEEP</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>20.88</v>
+        <v>14.41</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>46171.5937962963</v>
+        <v>46170.85421296296</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>46175.62796296296</v>
+        <v>46176.69795138889</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>bt_s14_family</t>
+          <t>live_s14_family</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>BUY_ENGULF</t>
+          <t>SELL_ENGULF</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>35.61</v>
+        <v>20.88</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>46177.21875</v>
+        <v>46171.5937962963</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>46178.55208333334</v>
+        <v>46175.62796296296</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>mismatch_s14_family</t>
+          <t>bt_s14_family</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>SELL_ENGULF</t>
+          <t>BUY_ENGULF</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>12.38</v>
+        <v>35.61</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>46171.4062962963</v>
+        <v>46177.21875</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>46171.4062962963</v>
+        <v>46178.55208333334</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>s14_family_mismatch</t>
+          <t>mismatch_s14_family</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>SELL_ENGULF</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -12405,8 +12405,37 @@
         <v>46171.4062962963</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>s14_family_mismatch</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>46171.4062962963</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>46171.4062962963</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G47"/>
+  <autoFilter ref="A1:G48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>